--- a/実装ノート.xlsx
+++ b/実装ノート.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4721A667-BB05-49ED-9EA7-84814ECCA1D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29F99967-6F77-4AD8-A35D-659206FC4EA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="1080" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Note" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="56">
   <si>
     <t>３Ｄキャノン実装ノート</t>
     <rPh sb="6" eb="8">
@@ -127,16 +127,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>複数種類の敵</t>
-    <rPh sb="0" eb="4">
-      <t>フクスウシュルイ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>テキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>03</t>
   </si>
   <si>
@@ -185,16 +175,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>複数種類の弾</t>
-    <rPh sb="0" eb="4">
-      <t>フクスウシュルイ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>タマ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>05</t>
   </si>
   <si>
@@ -220,12 +200,350 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>弾が発射されること</t>
+    <rPh sb="0" eb="1">
+      <t>タマ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ハッシャ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>07</t>
+  </si>
+  <si>
+    <t>弾が砲身の向きに発射されること</t>
+    <rPh sb="0" eb="1">
+      <t>タマ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ホウシン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ハッシャ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カメラシェイク</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>08</t>
+  </si>
+  <si>
+    <t>弾に重力がかかっていること</t>
+    <rPh sb="0" eb="1">
+      <t>タマ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Effekseerによる３Ｄエフェクト再生</t>
+    <rPh sb="8" eb="10">
+      <t>サイセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09</t>
+  </si>
+  <si>
+    <t>弾とステージモデルとの衝突判定</t>
+    <rPh sb="0" eb="1">
+      <t>タマ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ショウトツ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>弾の爆発アニメーション</t>
+    <rPh sb="0" eb="1">
+      <t>タマ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>バクハツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>敵が描画され、右方向に移動すること</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ビョウガ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>ミギホウコウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>イドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>敵が歩くアニメーションを行っていること</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>アル</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>弾と敵との衝突判定</t>
+    <rPh sb="0" eb="1">
+      <t>タマ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ショウトツ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>ゲームオーバー判定</t>
+    <rPh sb="7" eb="9">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>・</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チェックされていない通常項目は、評価対象外とし減点となります</t>
+    <rPh sb="10" eb="12">
+      <t>ツウジョウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ヒョウカ</t>
+    </rPh>
+    <rPh sb="18" eb="21">
+      <t>タイショウガイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ゲンテン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チェックされている通常項目は、正常に実装されていない場合、減点となります</t>
+    <rPh sb="9" eb="11">
+      <t>ツウジョウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>セイジョウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ゲンテン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>グレーの通常項目とExtra項目については、チェックされていなくても減点にはなりません</t>
+    <rPh sb="4" eb="6">
+      <t>ツウジョウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ゲンテン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>項目にチェックされ、正常に実装されていれば、加点とします</t>
+    <rPh sb="0" eb="2">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>セイジョウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>カテン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>その他、出席状況や平常点を考慮し、課題の評価点とします</t>
+    <rPh sb="2" eb="3">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シュッセキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヘイジョウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>コウリョ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ヒョウカ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>テン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>特筆事項</t>
+    <rPh sb="0" eb="2">
+      <t>トクヒツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>✅</t>
+  </si>
+  <si>
+    <t>・LeftShiftキーで砲身回転速度が上昇します。</t>
+    <rPh sb="13" eb="15">
+      <t>ホウシン</t>
+    </rPh>
+    <rPh sb="15" eb="19">
+      <t>カイテンソクド</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>弾の発射軌道を描画</t>
+    <rPh sb="0" eb="1">
+      <t>タマ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ハッシャ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>キドウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ビョウガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>城のHP追加・描画</t>
+    <rPh sb="0" eb="1">
+      <t>シロ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ビョウガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>中川原諒</t>
+    <rPh sb="0" eb="4">
+      <t>ナカガワラリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>計２種類の敵</t>
+    <rPh sb="0" eb="1">
+      <t>ケイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シュルイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>機能が異なる複数種類の弾</t>
     <rPh sb="0" eb="2">
       <t>キノウ</t>
     </rPh>
-    <rPh sb="6" eb="10">
-      <t>フクスウシュルイ</t>
+    <rPh sb="3" eb="4">
+      <t>コト</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>フクスウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>シュルイ</t>
     </rPh>
     <rPh sb="11" eb="12">
       <t>タマ</t>
@@ -233,308 +551,19 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>06</t>
-  </si>
-  <si>
-    <t>弾が発射されること</t>
-    <rPh sb="0" eb="1">
+    <t>城がダメージを受けると、城のみダメージ演出</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>複数種類の弾</t>
+    <rPh sb="0" eb="2">
+      <t>フクスウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シュルイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
       <t>タマ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ハッシャ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ステージ移行</t>
-    <rPh sb="4" eb="6">
-      <t>イコウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>07</t>
-  </si>
-  <si>
-    <t>弾が砲身の向きに発射されること</t>
-    <rPh sb="0" eb="1">
-      <t>タマ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ホウシン</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ム</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ハッシャ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>カメラシェイク</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>08</t>
-  </si>
-  <si>
-    <t>弾に重力がかかっていること</t>
-    <rPh sb="0" eb="1">
-      <t>タマ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Effekseerによる３Ｄエフェクト再生</t>
-    <rPh sb="8" eb="10">
-      <t>サイセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>09</t>
-  </si>
-  <si>
-    <t>弾とステージモデルとの衝突判定</t>
-    <rPh sb="0" eb="1">
-      <t>タマ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ショウトツ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ハンテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>弾の爆発アニメーション</t>
-    <rPh sb="0" eb="1">
-      <t>タマ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>バクハツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>敵が描画され、右方向に移動すること</t>
-    <rPh sb="0" eb="1">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ビョウガ</t>
-    </rPh>
-    <rPh sb="7" eb="10">
-      <t>ミギホウコウ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>イドウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>敵が歩くアニメーションを行っていること</t>
-    <rPh sb="0" eb="1">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>アル</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>オコナ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>弾と敵との衝突判定</t>
-    <rPh sb="0" eb="1">
-      <t>タマ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ショウトツ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ハンテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>ゲームオーバー判定</t>
-    <rPh sb="7" eb="9">
-      <t>ハンテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>・</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>チェックされていない通常項目は、評価対象外とし減点となります</t>
-    <rPh sb="10" eb="12">
-      <t>ツウジョウ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>コウモク</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ヒョウカ</t>
-    </rPh>
-    <rPh sb="18" eb="21">
-      <t>タイショウガイ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>ゲンテン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>チェックされている通常項目は、正常に実装されていない場合、減点となります</t>
-    <rPh sb="9" eb="11">
-      <t>ツウジョウ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>コウモク</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>セイジョウ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>ジッソウ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>ゲンテン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>グレーの通常項目とExtra項目については、チェックされていなくても減点にはなりません</t>
-    <rPh sb="4" eb="6">
-      <t>ツウジョウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>コウモク</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>コウモク</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>ゲンテン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>項目にチェックされ、正常に実装されていれば、加点とします</t>
-    <rPh sb="0" eb="2">
-      <t>コウモク</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>セイジョウ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ジッソウ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>カテン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>その他、出席状況や平常点を考慮し、課題の評価点とします</t>
-    <rPh sb="2" eb="3">
-      <t>タ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>シュッセキ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ジョウキョウ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ヘイジョウ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>テン</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>コウリョ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>カダイ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ヒョウカ</t>
-    </rPh>
-    <rPh sb="22" eb="23">
-      <t>テン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>特筆事項</t>
-    <rPh sb="0" eb="2">
-      <t>トクヒツ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジコウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>✅</t>
-  </si>
-  <si>
-    <t>・LeftShiftキーで砲身回転速度が上昇します。</t>
-    <rPh sb="13" eb="15">
-      <t>ホウシン</t>
-    </rPh>
-    <rPh sb="15" eb="19">
-      <t>カイテンソクド</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ジョウショウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>弾の発射軌道を描画</t>
-    <rPh sb="0" eb="1">
-      <t>タマ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ハッシャ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>キドウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ビョウガ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -956,7 +985,9 @@
     <col min="5" max="5" width="2.5" style="2" customWidth="1"/>
     <col min="6" max="18" width="2.5" style="2"/>
     <col min="19" max="19" width="2.5" style="2" customWidth="1"/>
-    <col min="20" max="16384" width="2.5" style="2"/>
+    <col min="20" max="30" width="2.5" style="2"/>
+    <col min="31" max="31" width="6.3984375" style="2" customWidth="1"/>
+    <col min="32" max="16384" width="2.5" style="2"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:31" ht="23.4" x14ac:dyDescent="0.3">
@@ -971,7 +1002,9 @@
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
-      <c r="G6" s="10"/>
+      <c r="G6" s="10">
+        <v>2416026</v>
+      </c>
       <c r="H6" s="10"/>
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
@@ -983,7 +1016,9 @@
       <c r="P6" s="9"/>
       <c r="Q6" s="9"/>
       <c r="R6" s="9"/>
-      <c r="S6" s="10"/>
+      <c r="S6" s="10" t="s">
+        <v>51</v>
+      </c>
       <c r="T6" s="10"/>
       <c r="U6" s="10"/>
       <c r="V6" s="10"/>
@@ -1067,7 +1102,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>9</v>
@@ -1084,7 +1119,9 @@
       <c r="O11" s="7"/>
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
-      <c r="R11" s="6"/>
+      <c r="R11" s="6" t="s">
+        <v>47</v>
+      </c>
       <c r="S11" s="7" t="s">
         <v>10</v>
       </c>
@@ -1106,7 +1143,7 @@
         <v>11</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>12</v>
@@ -1123,9 +1160,11 @@
       <c r="O12" s="7"/>
       <c r="P12" s="7"/>
       <c r="Q12" s="7"/>
-      <c r="R12" s="6"/>
+      <c r="R12" s="6" t="s">
+        <v>47</v>
+      </c>
       <c r="S12" s="7" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="T12" s="7"/>
       <c r="U12" s="7"/>
@@ -1142,13 +1181,13 @@
     </row>
     <row r="13" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C13" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>14</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>15</v>
       </c>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
@@ -1162,9 +1201,11 @@
       <c r="O13" s="7"/>
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
-      <c r="R13" s="6"/>
+      <c r="R13" s="6" t="s">
+        <v>47</v>
+      </c>
       <c r="S13" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T13" s="7"/>
       <c r="U13" s="7"/>
@@ -1181,13 +1222,13 @@
     </row>
     <row r="14" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C14" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" s="7" t="s">
         <v>17</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>18</v>
       </c>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
@@ -1201,9 +1242,11 @@
       <c r="O14" s="7"/>
       <c r="P14" s="7"/>
       <c r="Q14" s="7"/>
-      <c r="R14" s="6"/>
+      <c r="R14" s="6" t="s">
+        <v>47</v>
+      </c>
       <c r="S14" s="7" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="T14" s="7"/>
       <c r="U14" s="7"/>
@@ -1220,13 +1263,13 @@
     </row>
     <row r="15" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C15" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
@@ -1240,9 +1283,11 @@
       <c r="O15" s="7"/>
       <c r="P15" s="7"/>
       <c r="Q15" s="7"/>
-      <c r="R15" s="6"/>
+      <c r="R15" s="6" t="s">
+        <v>47</v>
+      </c>
       <c r="S15" s="7" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="T15" s="7"/>
       <c r="U15" s="7"/>
@@ -1259,13 +1304,13 @@
     </row>
     <row r="16" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C16" s="5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
@@ -1279,9 +1324,11 @@
       <c r="O16" s="7"/>
       <c r="P16" s="7"/>
       <c r="Q16" s="7"/>
-      <c r="R16" s="6"/>
+      <c r="R16" s="6" t="s">
+        <v>47</v>
+      </c>
       <c r="S16" s="7" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T16" s="7"/>
       <c r="U16" s="7"/>
@@ -1298,13 +1345,13 @@
     </row>
     <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="5" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F17" s="7"/>
       <c r="G17" s="7"/>
@@ -1319,10 +1366,10 @@
       <c r="P17" s="7"/>
       <c r="Q17" s="7"/>
       <c r="R17" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="S17" s="7" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="T17" s="7"/>
       <c r="U17" s="7"/>
@@ -1339,13 +1386,13 @@
     </row>
     <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="5" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
@@ -1361,7 +1408,7 @@
       <c r="Q18" s="7"/>
       <c r="R18" s="6"/>
       <c r="S18" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="T18" s="7"/>
       <c r="U18" s="7"/>
@@ -1378,13 +1425,13 @@
     </row>
     <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="5" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F19" s="7"/>
       <c r="G19" s="7"/>
@@ -1398,9 +1445,7 @@
       <c r="O19" s="7"/>
       <c r="P19" s="7"/>
       <c r="Q19" s="7"/>
-      <c r="R19" s="6" t="s">
-        <v>51</v>
-      </c>
+      <c r="R19" s="6"/>
       <c r="S19" s="7" t="s">
         <v>53</v>
       </c>
@@ -1419,13 +1464,13 @@
     </row>
     <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="5" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
@@ -1440,7 +1485,9 @@
       <c r="P20" s="7"/>
       <c r="Q20" s="7"/>
       <c r="R20" s="6"/>
-      <c r="S20" s="7"/>
+      <c r="S20" s="7" t="s">
+        <v>50</v>
+      </c>
       <c r="T20" s="7"/>
       <c r="U20" s="7"/>
       <c r="V20" s="7"/>
@@ -1456,13 +1503,13 @@
     </row>
     <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
@@ -1477,7 +1524,9 @@
       <c r="P21" s="7"/>
       <c r="Q21" s="7"/>
       <c r="R21" s="6"/>
-      <c r="S21" s="7"/>
+      <c r="S21" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="T21" s="7"/>
       <c r="U21" s="7"/>
       <c r="V21" s="7"/>
@@ -1493,13 +1542,13 @@
     </row>
     <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F22" s="7"/>
       <c r="G22" s="7"/>
@@ -1530,13 +1579,13 @@
     </row>
     <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F23" s="7"/>
       <c r="G23" s="7"/>
@@ -1567,13 +1616,13 @@
     </row>
     <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F24" s="7"/>
       <c r="G24" s="7"/>
@@ -1604,7 +1653,7 @@
     </row>
     <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="7"/>
@@ -1637,44 +1686,44 @@
     </row>
     <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="D27" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="D28" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="D29" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="E30" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="D31" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C33" s="11" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D33" s="11"/>
       <c r="E33" s="11"/>
@@ -1707,7 +1756,7 @@
     </row>
     <row r="34" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C34" s="10" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D34" s="10"/>
       <c r="E34" s="10"/>
